--- a/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Syracuse_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Cup - Hot (20oz)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>83.13</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>83.13</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>83.13</v>
+      </c>
+      <c r="E2" t="n">
+        <v>83.13</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Cup - Hot (16oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>70.09</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>70.09</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="E3" t="n">
+        <v>70.09</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Cup - Hot (12oz)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>62.78</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>62.78</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="E4" t="n">
+        <v>62.78</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Wrap - Foil (9" x 10.75")</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>104.47</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>104.47</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>104.47</v>
+      </c>
+      <c r="E5" t="n">
+        <v>104.47</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Wrap - Cold Sandwich (18" x 18")</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>66.52</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>66.52</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>66.52</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Napkin - Dispenser</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30.94</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Bag - Paper (10#)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>17.60</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>35.20</t>
-        </is>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>35.2</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Bag - Paper (6#)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25.56</v>
       </c>
     </row>
   </sheetData>
